--- a/ilanlar3.xlsx
+++ b/ilanlar3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minel/PycharmProjects/WEBKAZIMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44675237-7931-7047-9836-1F1736BB329F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DF51B2-66E7-EF40-A312-4A19C61DD56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="25600" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4427,6 +4427,8 @@
   <dimension ref="A1:W505"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="68" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
